--- a/resources/templates/standard/H3100-04.xlsx
+++ b/resources/templates/standard/H3100-04.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>종업원 만족도 조사 설문지</t>
   </si>
@@ -757,11 +760,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -852,7 +857,7 @@
     </row>
     <row r="5" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -877,7 +882,7 @@
     </row>
     <row r="6" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -902,7 +907,7 @@
     </row>
     <row r="7" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -927,7 +932,7 @@
     </row>
     <row r="8" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -975,10 +980,10 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -986,7 +991,7 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -994,7 +999,7 @@
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O10" s="10"/>
       <c r="P10" s="10"/>
@@ -1048,22 +1053,22 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K12" s="12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L12" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N12" s="10"/>
       <c r="O12" s="10"/>
@@ -1079,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -1106,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -1133,7 +1138,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -1160,7 +1165,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -1187,7 +1192,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -1214,7 +1219,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -1241,7 +1246,7 @@
         <v>7</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -1268,7 +1273,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -1295,7 +1300,7 @@
         <v>9</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -1322,7 +1327,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="20"/>
       <c r="D22" s="20"/>
@@ -1346,7 +1351,7 @@
     </row>
     <row r="23" ht="20.1" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B23" s="23"/>
       <c r="C23" s="23"/>
@@ -1365,7 +1370,7 @@
       <c r="P23" s="24"/>
       <c r="Q23" s="24"/>
       <c r="R23" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S23" s="25"/>
       <c r="T23" s="25"/>
